--- a/data/q1_3.xlsx
+++ b/data/q1_3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\INE\Indice_de_Bem_Estar\IBE_dashboard\data\out2pe\out2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACC919F-18F9-488B-A69D-13077B706328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C968A4-5D59-4009-B053-BB2DB5E8439F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3765" yWindow="735" windowWidth="21660" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="392">
   <si>
     <t>ord</t>
   </si>
@@ -101,18 +101,12 @@
     <t>2022</t>
   </si>
   <si>
-    <t>Rendimento monetário disponível mediano por adulto equivalente (preços constantes, 2015)</t>
-  </si>
-  <si>
     <t>Património financeiro líquido dos particulares (per capita, preços constantes, 2015)</t>
   </si>
   <si>
     <t>Património total líquido dos particulares (per capita, preços constantes, 2015)</t>
   </si>
   <si>
-    <t>Despesa de consumo final das famílias per capita  (preços constantes, 2015)</t>
-  </si>
-  <si>
     <t>Desigualdade na distribuição do rendimento (S80/S20)</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>Proporção de pessoas satisfeitas com o estado atual da economia do país</t>
   </si>
   <si>
-    <t>Rendimento líquido mediano dos trabalhadores por conta de outrém (preços constantes, 2015)</t>
-  </si>
-  <si>
     <t>Taxa de risco de pobreza (60% da mediana), após transferências sociais</t>
   </si>
   <si>
@@ -137,18 +128,12 @@
     <t>Intensidade laboral per capita muito reduzida</t>
   </si>
   <si>
-    <t>Taxa de privação material</t>
-  </si>
-  <si>
     <t>Endividamento dos particulares (dívida financeira) em percentagem do rendimento disponível</t>
   </si>
   <si>
     <t>Taxa de sobrecarga das despesas em habitação</t>
   </si>
   <si>
-    <t>Taxa de emprego (15 e mais anos)</t>
-  </si>
-  <si>
     <t>Proporção de trabalhadores com 25 e mais anos com contrato de trabalho a termo</t>
   </si>
   <si>
@@ -161,9 +146,6 @@
     <t>Taxa de desemprego da população com nível de escolaridade completo correspondente ao ensino superior</t>
   </si>
   <si>
-    <t>Taxa de desemprego da população dos 15 aos 34 anos</t>
-  </si>
-  <si>
     <t>Inativos por 100 empregados</t>
   </si>
   <si>
@@ -176,9 +158,6 @@
     <t>Proporção de pessoas que pensam ser provável ou muito provável perder o seu emprego nos seis meses seguintes</t>
   </si>
   <si>
-    <t>Proporção da população desempregada inscrita num Centro de Emprego do IEFP que não recebe nenhum tipo de subsídio relacionado com o desemprego</t>
-  </si>
-  <si>
     <t>Esperança de vida à nascença</t>
   </si>
   <si>
@@ -188,12 +167,6 @@
     <t>Esperança de vida em saúde</t>
   </si>
   <si>
-    <t>Taxa de mortalidade padronizada (&lt;65 anos), por doenças do aparelho circulatório, por 100 000 habitantes</t>
-  </si>
-  <si>
-    <t>Taxa de mortalidade padronizada, por tumores malignos, por 100 000 habitantes</t>
-  </si>
-  <si>
     <t>Proporção da população residente que avalia o seu estado de saúde como bom ou muito bom</t>
   </si>
   <si>
@@ -215,9 +188,6 @@
     <t>Abandono precoce de educação e formação (18-24 anos)</t>
   </si>
   <si>
-    <t>Proporção de pessoas (30-34 anos), com nível de escolaridade completo correspondente ao ensino superior</t>
-  </si>
-  <si>
     <t>Número médio de anos de escolaridade completa da população ativa</t>
   </si>
   <si>
@@ -302,9 +272,6 @@
     <t>Total de emissões de gases com efeito de estufa</t>
   </si>
   <si>
-    <t>Exposição à poluição no ar a partículas PM2,5 (µg/m3)</t>
-  </si>
-  <si>
     <t>População que reporta problemas de ruído na vizinhança da sua residência</t>
   </si>
   <si>
@@ -1206,13 +1173,49 @@
   </si>
   <si>
     <t>Pop. reporting exposure to pollution, grime or other env. problems</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Rendimento monetário disponível mediano por adulto equivalente (PPC)</t>
+  </si>
+  <si>
+    <t>Despesa de consumo individual per capita  (PPC)</t>
+  </si>
+  <si>
+    <t>Rendimento líquido mediano dos trabalhadores por conta de outrém (PPC)</t>
+  </si>
+  <si>
+    <t>Taxa de privação material e social</t>
+  </si>
+  <si>
+    <t>Taxa de emprego</t>
+  </si>
+  <si>
+    <t>Taxa de desemprego da população dos 16 aos 34 anos</t>
+  </si>
+  <si>
+    <t>Proporção da população desempregada inscrita num Centro de Emprego que não recebe nenhum tipo de subsídio relacionado com o desemprego</t>
+  </si>
+  <si>
+    <t>Taxa de mortalidade padronizada (&lt;65 anos), por doenças do aparelho circulatório, por 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Taxa de mortalidade padronizada, por tumores malignos, por 100 mil habitantes</t>
+  </si>
+  <si>
+    <t>Proporção de pessoas (30-34 anos) com nível de escolaridade completo correspondente ao ensino superior</t>
+  </si>
+  <si>
+    <t>Mortes prematuras devidas à poluição do ar por 100 mil habitantes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,6 +1239,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1245,7 +1257,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1253,11 +1265,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1265,6 +1286,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1569,24 +1593,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA85"/>
+  <dimension ref="A1:AB85"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="119.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="138.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="132.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="138.140625" customWidth="1"/>
+    <col min="8" max="8" width="132.140625" customWidth="1"/>
+    <col min="9" max="27" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -1595,13 +1620,13 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -1660,8 +1685,11 @@
       <c r="AA1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>380</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1669,79 +1697,85 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>381</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="H2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K2">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="M2">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="N2">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="O2">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q2">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="S2">
-        <v>4.0999999999999996</v>
+        <v>10.4</v>
       </c>
       <c r="T2">
-        <v>7.4</v>
+        <v>12.8</v>
       </c>
       <c r="U2">
-        <v>7</v>
+        <v>12.9</v>
       </c>
       <c r="V2">
-        <v>5.6</v>
+        <v>12.8</v>
       </c>
       <c r="W2">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="Y2">
-        <v>16.2</v>
+        <v>20.8</v>
       </c>
       <c r="Z2">
-        <v>14.3</v>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="AA2">
+        <v>25.9</v>
+      </c>
+      <c r="AB2">
+        <v>27.9</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1749,22 +1783,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="G3" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="H3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="I3">
         <v>1.4</v>
@@ -1773,58 +1807,61 @@
         <v>1.7</v>
       </c>
       <c r="K3">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L3">
         <v>2.2000000000000002</v>
       </c>
       <c r="M3">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
         <v>1.7</v>
       </c>
       <c r="R3">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T3">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="U3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="V3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W3">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="Y3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Z3">
+        <v>10.7</v>
+      </c>
+      <c r="AA3">
         <v>9</v>
       </c>
-      <c r="Z3">
-        <v>10.3</v>
-      </c>
-      <c r="AA3">
-        <v>8.5</v>
+      <c r="AB3">
+        <v>9.1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1832,43 +1869,43 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G4" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="H4" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="I4">
         <v>4</v>
       </c>
       <c r="J4">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="L4">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="O4">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="P4">
         <v>3</v>
@@ -1880,7 +1917,7 @@
         <v>0.1</v>
       </c>
       <c r="S4">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="T4">
         <v>3.2</v>
@@ -1889,25 +1926,28 @@
         <v>4.8</v>
       </c>
       <c r="V4">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W4">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="Z4">
-        <v>18.600000000000001</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="AA4">
-        <v>17.3</v>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AB4">
+        <v>18.2</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -1915,82 +1955,85 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>382</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="G5" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="H5" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="I5">
-        <v>15.9</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
-        <v>24.3</v>
+        <v>8.4</v>
       </c>
       <c r="K5">
-        <v>28.6</v>
+        <v>11.7</v>
       </c>
       <c r="L5">
-        <v>30.8</v>
+        <v>14</v>
       </c>
       <c r="M5">
-        <v>33.200000000000003</v>
+        <v>17.3</v>
       </c>
       <c r="N5">
-        <v>24.3</v>
+        <v>13.4</v>
       </c>
       <c r="O5">
-        <v>28.5</v>
+        <v>16.2</v>
       </c>
       <c r="P5">
-        <v>18.5</v>
+        <v>13.4</v>
       </c>
       <c r="Q5">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="R5">
-        <v>14.6</v>
+        <v>13.4</v>
       </c>
       <c r="S5">
-        <v>19.7</v>
+        <v>15.6</v>
       </c>
       <c r="T5">
-        <v>24.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="U5">
-        <v>27.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="V5">
-        <v>28.2</v>
+        <v>22.3</v>
       </c>
       <c r="W5">
-        <v>35.200000000000003</v>
+        <v>26.8</v>
       </c>
       <c r="X5">
-        <v>40.4</v>
+        <v>30.2</v>
       </c>
       <c r="Y5">
-        <v>25.4</v>
+        <v>23.5</v>
       </c>
       <c r="Z5">
-        <v>34.6</v>
+        <v>31.3</v>
       </c>
       <c r="AA5">
-        <v>42.2</v>
+        <v>44.1</v>
+      </c>
+      <c r="AB5">
+        <v>52.5</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -1998,22 +2041,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G6" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="H6" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2069,8 +2112,14 @@
       <c r="Z6">
         <v>51.8</v>
       </c>
+      <c r="AA6">
+        <v>38.1</v>
+      </c>
+      <c r="AB6">
+        <v>41.1</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -2078,22 +2127,22 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="G7" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H7" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2149,8 +2198,14 @@
       <c r="Z7">
         <v>41.5</v>
       </c>
+      <c r="AA7">
+        <v>29.9</v>
+      </c>
+      <c r="AB7">
+        <v>31.6</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -2158,82 +2213,85 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G8" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="H8" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="K8">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="L8">
-        <v>10.4</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="M8">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="N8">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="O8">
-        <v>31.3</v>
+        <v>30.6</v>
       </c>
       <c r="P8">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="Q8">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="R8">
-        <v>34.5</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="S8">
-        <v>33.9</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="T8">
-        <v>37.799999999999997</v>
+        <v>37</v>
       </c>
       <c r="U8">
-        <v>37.1</v>
+        <v>36.4</v>
       </c>
       <c r="V8">
-        <v>41.7</v>
+        <v>40.9</v>
       </c>
       <c r="W8">
-        <v>41</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="X8">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="Y8">
-        <v>47.6</v>
+        <v>46.6</v>
       </c>
       <c r="Z8">
-        <v>49.5</v>
+        <v>50.7</v>
       </c>
       <c r="AA8">
-        <v>50.7</v>
+        <v>55.4</v>
+      </c>
+      <c r="AB8">
+        <v>56.4</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -2241,22 +2299,22 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G9" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="H9" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2310,10 +2368,16 @@
         <v>25.3</v>
       </c>
       <c r="Z9">
-        <v>25.3</v>
+        <v>23.2</v>
+      </c>
+      <c r="AA9">
+        <v>21.2</v>
+      </c>
+      <c r="AB9">
+        <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -2321,79 +2385,85 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>383</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G10" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="H10" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="I10">
-        <v>4.5999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="J10">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>4.9000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="L10">
-        <v>4.9000000000000004</v>
+        <v>3.5</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N10">
-        <v>9.1999999999999993</v>
+        <v>6.6</v>
       </c>
       <c r="O10">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="P10">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q10">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="R10">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="S10">
-        <v>6.4</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="T10">
-        <v>8.8000000000000007</v>
+        <v>11.2</v>
       </c>
       <c r="U10">
-        <v>7.3</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="V10">
-        <v>5.8</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="W10">
-        <v>8.4</v>
+        <v>12.9</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
-        <v>13.8</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="Z10">
-        <v>10.1</v>
+        <v>15.2</v>
+      </c>
+      <c r="AA10">
+        <v>23.1</v>
+      </c>
+      <c r="AB10">
+        <v>25.3</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -2401,22 +2471,22 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="G11" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="H11" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="I11">
         <v>22.7</v>
@@ -2472,8 +2542,14 @@
       <c r="Z11">
         <v>46.1</v>
       </c>
+      <c r="AA11">
+        <v>41.4</v>
+      </c>
+      <c r="AB11">
+        <v>42.4</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -2481,22 +2557,22 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="H12" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="I12">
         <v>27.7</v>
@@ -2552,8 +2628,14 @@
       <c r="Z12">
         <v>52</v>
       </c>
+      <c r="AA12">
+        <v>29.9</v>
+      </c>
+      <c r="AB12">
+        <v>29.8</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -2561,79 +2643,85 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G13" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="H13" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="I13">
-        <v>80.2</v>
+        <v>79</v>
       </c>
       <c r="J13">
-        <v>75.400000000000006</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="K13">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="L13">
+        <v>76.5</v>
+      </c>
+      <c r="M13">
         <v>70.599999999999994</v>
       </c>
-      <c r="L13">
-        <v>77.8</v>
-      </c>
-      <c r="M13">
-        <v>72.2</v>
-      </c>
       <c r="N13">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
       <c r="O13">
-        <v>61.9</v>
+        <v>59.7</v>
       </c>
       <c r="P13">
-        <v>47.6</v>
+        <v>44.5</v>
       </c>
       <c r="Q13">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="R13">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="S13">
-        <v>46.8</v>
+        <v>43.7</v>
       </c>
       <c r="T13">
-        <v>60.3</v>
+        <v>58</v>
       </c>
       <c r="U13">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="V13">
-        <v>73</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="W13">
-        <v>78.599999999999994</v>
+        <v>77.3</v>
       </c>
       <c r="X13">
-        <v>88.1</v>
+        <v>87.4</v>
       </c>
       <c r="Y13">
-        <v>85.7</v>
+        <v>84.9</v>
       </c>
       <c r="Z13">
-        <v>83.3</v>
+        <v>82.4</v>
+      </c>
+      <c r="AA13">
+        <v>76.5</v>
+      </c>
+      <c r="AB13">
+        <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -2641,22 +2729,22 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="F14" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="G14" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="I14">
         <v>21.8</v>
@@ -2692,16 +2780,16 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="U14">
-        <v>33.299999999999997</v>
+        <v>32.9</v>
       </c>
       <c r="V14">
-        <v>42</v>
+        <v>41.2</v>
       </c>
       <c r="W14">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="X14">
         <v>56.8</v>
@@ -2715,8 +2803,11 @@
       <c r="AA14">
         <v>62.1</v>
       </c>
+      <c r="AB14">
+        <v>62.1</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>16</v>
       </c>
@@ -2724,82 +2815,82 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G15" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="H15" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="I15">
-        <v>66.099999999999994</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="J15">
-        <v>63.2</v>
+        <v>62.7</v>
       </c>
       <c r="K15">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="L15">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="M15">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="N15">
+        <v>55.8</v>
+      </c>
+      <c r="O15">
+        <v>56</v>
+      </c>
+      <c r="P15">
         <v>55.9</v>
       </c>
-      <c r="O15">
-        <v>56.3</v>
-      </c>
-      <c r="P15">
-        <v>56.5</v>
-      </c>
       <c r="Q15">
-        <v>58.4</v>
+        <v>57.8</v>
       </c>
       <c r="R15">
-        <v>60.2</v>
+        <v>59.7</v>
       </c>
       <c r="S15">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
       <c r="T15">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="U15">
         <v>68.5</v>
       </c>
       <c r="V15">
-        <v>70.099999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="W15">
-        <v>72.3</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="X15">
-        <v>74.099999999999994</v>
+        <v>73.7</v>
       </c>
       <c r="Y15">
         <v>72.400000000000006</v>
       </c>
       <c r="Z15">
-        <v>72.8</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="AA15">
-        <v>75.8</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>17</v>
       </c>
@@ -2807,82 +2898,85 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="H16" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="I16">
-        <v>79.3</v>
+        <v>77.5</v>
       </c>
       <c r="J16">
-        <v>81.599999999999994</v>
+        <v>80</v>
       </c>
       <c r="K16">
-        <v>80.5</v>
+        <v>78.8</v>
       </c>
       <c r="L16">
-        <v>63.8</v>
+        <v>60.6</v>
       </c>
       <c r="M16">
-        <v>62.6</v>
+        <v>59.4</v>
       </c>
       <c r="N16">
+        <v>68.8</v>
+      </c>
+      <c r="O16">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="P16">
+        <v>61.9</v>
+      </c>
+      <c r="Q16">
+        <v>55</v>
+      </c>
+      <c r="R16">
+        <v>55</v>
+      </c>
+      <c r="S16">
+        <v>49.4</v>
+      </c>
+      <c r="T16">
+        <v>50</v>
+      </c>
+      <c r="U16">
+        <v>60</v>
+      </c>
+      <c r="V16">
+        <v>65</v>
+      </c>
+      <c r="W16">
         <v>71.3</v>
       </c>
-      <c r="O16">
-        <v>82.2</v>
-      </c>
-      <c r="P16">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="Q16">
-        <v>58.6</v>
-      </c>
-      <c r="R16">
-        <v>58.6</v>
-      </c>
-      <c r="S16">
-        <v>53.4</v>
-      </c>
-      <c r="T16">
-        <v>54</v>
-      </c>
-      <c r="U16">
-        <v>63.2</v>
-      </c>
-      <c r="V16">
-        <v>67.8</v>
-      </c>
-      <c r="W16">
-        <v>73.599999999999994</v>
-      </c>
       <c r="X16">
-        <v>73.599999999999994</v>
+        <v>71.3</v>
       </c>
       <c r="Y16">
-        <v>82.8</v>
+        <v>81.3</v>
       </c>
       <c r="Z16">
-        <v>72.400000000000006</v>
+        <v>70</v>
       </c>
       <c r="AA16">
-        <v>77.599999999999994</v>
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AB16">
+        <v>76.2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>18</v>
       </c>
@@ -2890,82 +2984,85 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G17" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="I17">
-        <v>65.2</v>
+        <v>63.5</v>
       </c>
       <c r="J17">
-        <v>63.4</v>
+        <v>61.8</v>
       </c>
       <c r="K17">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
       <c r="L17">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
       <c r="M17">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
       <c r="N17">
-        <v>56.4</v>
+        <v>54.9</v>
       </c>
       <c r="O17">
-        <v>52</v>
+        <v>50.6</v>
       </c>
       <c r="P17">
-        <v>44.1</v>
+        <v>31.8</v>
       </c>
       <c r="Q17">
+        <v>22.3</v>
+      </c>
+      <c r="R17">
+        <v>19.3</v>
+      </c>
+      <c r="S17">
+        <v>26.2</v>
+      </c>
+      <c r="T17">
+        <v>30.9</v>
+      </c>
+      <c r="U17">
         <v>35.200000000000003</v>
       </c>
-      <c r="R17">
-        <v>30.4</v>
-      </c>
-      <c r="S17">
-        <v>34.4</v>
-      </c>
-      <c r="T17">
-        <v>37.4</v>
-      </c>
-      <c r="U17">
-        <v>40.5</v>
-      </c>
       <c r="V17">
-        <v>48</v>
+        <v>42.9</v>
       </c>
       <c r="W17">
-        <v>53.7</v>
+        <v>49.4</v>
       </c>
       <c r="X17">
-        <v>55.5</v>
+        <v>50.6</v>
       </c>
       <c r="Y17">
-        <v>47.6</v>
+        <v>44.2</v>
       </c>
       <c r="Z17">
-        <v>53.3</v>
+        <v>49.4</v>
       </c>
       <c r="AA17">
-        <v>58.6</v>
+        <v>54.9</v>
+      </c>
+      <c r="AB17">
+        <v>57.9</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>19</v>
       </c>
@@ -2973,34 +3070,34 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G18" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="H18" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="I18">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="J18">
-        <v>39.200000000000003</v>
+        <v>39.1</v>
       </c>
       <c r="K18">
         <v>35.1</v>
       </c>
       <c r="L18">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="M18">
         <v>23.5</v>
@@ -3009,46 +3106,49 @@
         <v>23.5</v>
       </c>
       <c r="O18">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P18">
-        <v>18.899999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="Q18">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="R18">
-        <v>19.5</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="S18">
-        <v>19.5</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="T18">
-        <v>17.2</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="U18">
-        <v>16.600000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="V18">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="W18">
-        <v>18.899999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="X18">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="Y18">
-        <v>33.4</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="Z18">
-        <v>35.700000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="AA18">
-        <v>41.5</v>
+        <v>40.9</v>
+      </c>
+      <c r="AB18">
+        <v>38.5</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>20</v>
       </c>
@@ -3056,82 +3156,85 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="G19" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="H19" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="I19">
-        <v>73.900000000000006</v>
+        <v>75.2</v>
       </c>
       <c r="J19">
-        <v>66.900000000000006</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="K19">
-        <v>66.900000000000006</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="L19">
-        <v>64.099999999999994</v>
+        <v>65.2</v>
       </c>
       <c r="M19">
-        <v>66.900000000000006</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="N19">
-        <v>54.2</v>
+        <v>55.3</v>
       </c>
       <c r="O19">
-        <v>44.4</v>
+        <v>45.4</v>
       </c>
       <c r="P19">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19">
-        <v>18.3</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="T19">
-        <v>29.6</v>
+        <v>30.5</v>
       </c>
       <c r="U19">
-        <v>39.4</v>
+        <v>40.4</v>
       </c>
       <c r="V19">
-        <v>55.6</v>
+        <v>56.7</v>
       </c>
       <c r="W19">
-        <v>69.7</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="X19">
-        <v>73.900000000000006</v>
+        <v>75.2</v>
       </c>
       <c r="Y19">
-        <v>71.099999999999994</v>
+        <v>72.3</v>
       </c>
       <c r="Z19">
-        <v>73.2</v>
+        <v>74.5</v>
       </c>
       <c r="AA19">
-        <v>77.5</v>
+        <v>78.7</v>
+      </c>
+      <c r="AB19">
+        <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>21</v>
       </c>
@@ -3139,22 +3242,22 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="G20" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="I20">
         <v>35.200000000000003</v>
@@ -3181,40 +3284,43 @@
         <v>25.7</v>
       </c>
       <c r="Q20">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="R20">
-        <v>10.3</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="S20">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="T20">
         <v>8.4</v>
       </c>
       <c r="U20">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="V20">
         <v>22.8</v>
       </c>
       <c r="W20">
-        <v>34.700000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="X20">
         <v>36.799999999999997</v>
       </c>
       <c r="Y20">
-        <v>54.6</v>
+        <v>55</v>
       </c>
       <c r="Z20">
-        <v>35.1</v>
+        <v>36.6</v>
       </c>
       <c r="AA20">
-        <v>32</v>
+        <v>32.200000000000003</v>
+      </c>
+      <c r="AB20">
+        <v>46.2</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>22</v>
       </c>
@@ -3222,82 +3328,85 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="G21" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="H21" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="I21">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="J21">
-        <v>57</v>
+        <v>56.6</v>
       </c>
       <c r="K21">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="L21">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="M21">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="N21">
-        <v>55.3</v>
+        <v>54.9</v>
       </c>
       <c r="O21">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="P21">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="Q21">
-        <v>8.8000000000000007</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
       <c r="S21">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="T21">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="U21">
-        <v>37.700000000000003</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="V21">
-        <v>54.4</v>
+        <v>54.9</v>
       </c>
       <c r="W21">
-        <v>64</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="X21">
-        <v>64.900000000000006</v>
+        <v>65.5</v>
       </c>
       <c r="Y21">
-        <v>60.5</v>
+        <v>59.3</v>
       </c>
       <c r="Z21">
-        <v>64.900000000000006</v>
+        <v>63.7</v>
       </c>
       <c r="AA21">
-        <v>71.900000000000006</v>
+        <v>71.7</v>
+      </c>
+      <c r="AB21">
+        <v>71.7</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>23</v>
       </c>
@@ -3305,82 +3414,85 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>386</v>
       </c>
       <c r="F22" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="H22" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="I22">
-        <v>77.099999999999994</v>
+        <v>77.2</v>
       </c>
       <c r="J22">
-        <v>66.900000000000006</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="K22">
-        <v>65.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="L22">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="M22">
-        <v>67.2</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="N22">
-        <v>53.9</v>
+        <v>54.3</v>
       </c>
       <c r="O22">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="P22">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
       <c r="S22">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="T22">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="U22">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="V22">
-        <v>53.4</v>
+        <v>53.6</v>
       </c>
       <c r="W22">
-        <v>66.3</v>
+        <v>67</v>
       </c>
       <c r="X22">
-        <v>71</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="Y22">
-        <v>58.4</v>
+        <v>58.1</v>
       </c>
       <c r="Z22">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="AA22">
-        <v>66.099999999999994</v>
+        <v>66.2</v>
+      </c>
+      <c r="AB22">
+        <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -3388,82 +3500,85 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G23" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="I23">
-        <v>74</v>
+        <v>72.3</v>
       </c>
       <c r="J23">
-        <v>74.099999999999994</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="K23">
-        <v>74.900000000000006</v>
+        <v>73.2</v>
       </c>
       <c r="L23">
-        <v>75.099999999999994</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="M23">
-        <v>74.8</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="N23">
-        <v>70</v>
+        <v>68.3</v>
       </c>
       <c r="O23">
-        <v>67.900000000000006</v>
+        <v>66.3</v>
       </c>
       <c r="P23">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="Q23">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R23">
-        <v>51.9</v>
+        <v>49.8</v>
       </c>
       <c r="S23">
-        <v>52.8</v>
+        <v>50.8</v>
       </c>
       <c r="T23">
-        <v>53.6</v>
+        <v>51.8</v>
       </c>
       <c r="U23">
-        <v>54.8</v>
+        <v>52.9</v>
       </c>
       <c r="V23">
-        <v>59.9</v>
+        <v>58</v>
       </c>
       <c r="W23">
-        <v>62.9</v>
+        <v>60.6</v>
       </c>
       <c r="X23">
-        <v>64.2</v>
+        <v>61.2</v>
       </c>
       <c r="Y23">
-        <v>53.7</v>
+        <v>54.2</v>
       </c>
       <c r="Z23">
-        <v>58.7</v>
+        <v>50.9</v>
       </c>
       <c r="AA23">
-        <v>63.6</v>
+        <v>56.3</v>
+      </c>
+      <c r="AB23">
+        <v>60.1</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -3471,82 +3586,85 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>203</v>
+      </c>
+      <c r="G24" t="s">
+        <v>278</v>
+      </c>
+      <c r="H24" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24">
         <v>95</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" t="s">
-        <v>214</v>
-      </c>
-      <c r="G24" t="s">
-        <v>289</v>
-      </c>
-      <c r="H24" t="s">
-        <v>289</v>
-      </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
-        <v>94.6</v>
+        <v>93.4</v>
       </c>
       <c r="K24">
-        <v>94.6</v>
+        <v>93.4</v>
       </c>
       <c r="L24">
-        <v>84.6</v>
+        <v>83.6</v>
       </c>
       <c r="M24">
-        <v>84.6</v>
+        <v>83.6</v>
       </c>
       <c r="N24">
-        <v>84.6</v>
+        <v>83.6</v>
       </c>
       <c r="O24">
-        <v>83.3</v>
+        <v>82.2</v>
       </c>
       <c r="P24">
+        <v>46.6</v>
+      </c>
+      <c r="Q24">
+        <v>32.9</v>
+      </c>
+      <c r="R24">
+        <v>30.1</v>
+      </c>
+      <c r="S24">
+        <v>35.6</v>
+      </c>
+      <c r="T24">
+        <v>37</v>
+      </c>
+      <c r="U24">
+        <v>42.5</v>
+      </c>
+      <c r="V24">
         <v>50.7</v>
       </c>
-      <c r="Q24">
-        <v>37.9</v>
-      </c>
-      <c r="R24">
-        <v>34.5</v>
-      </c>
-      <c r="S24">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="T24">
-        <v>41.2</v>
-      </c>
-      <c r="U24">
-        <v>45.8</v>
-      </c>
-      <c r="V24">
-        <v>54.3</v>
-      </c>
       <c r="W24">
-        <v>63.2</v>
+        <v>60.3</v>
       </c>
       <c r="X24">
-        <v>66.8</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="Y24">
-        <v>67.900000000000006</v>
+        <v>65.8</v>
       </c>
       <c r="Z24">
-        <v>70.5</v>
+        <v>68.5</v>
       </c>
       <c r="AA24">
-        <v>71.8</v>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="AB24">
+        <v>68.5</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -3554,22 +3672,22 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G25" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="H25" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="I25">
         <v>64.400000000000006</v>
@@ -3623,10 +3741,13 @@
         <v>55.3</v>
       </c>
       <c r="Z25">
-        <v>53.3</v>
+        <v>53.7</v>
+      </c>
+      <c r="AA25">
+        <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -3634,79 +3755,82 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="G26" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="H26" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="I26">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="J26">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="K26">
-        <v>36.200000000000003</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="L26">
-        <v>37.4</v>
+        <v>38.5</v>
       </c>
       <c r="M26">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="N26">
+        <v>41</v>
+      </c>
+      <c r="O26">
+        <v>42.3</v>
+      </c>
+      <c r="P26">
+        <v>41.5</v>
+      </c>
+      <c r="Q26">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="R26">
+        <v>39.9</v>
+      </c>
+      <c r="S26">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="T26">
+        <v>38.4</v>
+      </c>
+      <c r="U26">
+        <v>38.5</v>
+      </c>
+      <c r="V26">
+        <v>38.6</v>
+      </c>
+      <c r="W26">
         <v>38.700000000000003</v>
       </c>
-      <c r="N26">
-        <v>39.9</v>
-      </c>
-      <c r="O26">
-        <v>41.1</v>
-      </c>
-      <c r="P26">
-        <v>40.4</v>
-      </c>
-      <c r="Q26">
-        <v>39.6</v>
-      </c>
-      <c r="R26">
+      <c r="X26">
         <v>38.9</v>
       </c>
-      <c r="S26">
-        <v>38.1</v>
-      </c>
-      <c r="T26">
-        <v>37.4</v>
-      </c>
-      <c r="U26">
-        <v>35.4</v>
-      </c>
-      <c r="V26">
-        <v>33.5</v>
-      </c>
-      <c r="W26">
-        <v>31.5</v>
-      </c>
-      <c r="X26">
-        <v>29.6</v>
-      </c>
       <c r="Y26">
-        <v>27.6</v>
+        <v>39</v>
       </c>
       <c r="Z26">
-        <v>25.7</v>
+        <v>39.1</v>
+      </c>
+      <c r="AA26">
+        <v>39.1</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>29</v>
       </c>
@@ -3714,82 +3838,85 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>387</v>
       </c>
       <c r="F27" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G27" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="H27" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="I27">
-        <v>40</v>
+        <v>40.6</v>
       </c>
       <c r="J27">
-        <v>41.3</v>
+        <v>42</v>
       </c>
       <c r="K27">
-        <v>39.200000000000003</v>
+        <v>39.9</v>
       </c>
       <c r="L27">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="M27">
-        <v>37.6</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="N27">
-        <v>41.9</v>
+        <v>42.6</v>
       </c>
       <c r="O27">
-        <v>38.9</v>
+        <v>39.6</v>
       </c>
       <c r="P27">
-        <v>35.1</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="Q27">
-        <v>33.299999999999997</v>
+        <v>34</v>
       </c>
       <c r="R27">
-        <v>34.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="S27">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="T27">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
       <c r="U27">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="V27">
-        <v>29.7</v>
+        <v>30.7</v>
       </c>
       <c r="W27">
-        <v>36.5</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="X27">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="Y27">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="Z27">
-        <v>52.1</v>
+        <v>54.7</v>
       </c>
       <c r="AA27">
-        <v>45.9</v>
+        <v>47.6</v>
+      </c>
+      <c r="AB27">
+        <v>47.3</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>30</v>
       </c>
@@ -3797,22 +3924,22 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G28" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H28" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3869,10 +3996,13 @@
         <v>53.9</v>
       </c>
       <c r="AA28">
-        <v>53.9</v>
+        <v>53.7</v>
+      </c>
+      <c r="AB28">
+        <v>56.9</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>31</v>
       </c>
@@ -3880,82 +4010,85 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G29" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="H29" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="I29">
-        <v>38.200000000000003</v>
+        <v>36.4</v>
       </c>
       <c r="J29">
-        <v>47.1</v>
+        <v>45.5</v>
       </c>
       <c r="K29">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="L29">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="M29">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="N29">
-        <v>44.1</v>
+        <v>42.4</v>
       </c>
       <c r="O29">
-        <v>76.5</v>
+        <v>75.8</v>
       </c>
       <c r="P29">
-        <v>58.8</v>
+        <v>57.6</v>
       </c>
       <c r="Q29">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="R29">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="S29">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="T29">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="U29">
-        <v>55.9</v>
+        <v>54.5</v>
       </c>
       <c r="V29">
-        <v>70.599999999999994</v>
+        <v>69.7</v>
       </c>
       <c r="W29">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="X29">
-        <v>64.7</v>
+        <v>63.6</v>
       </c>
       <c r="Y29">
-        <v>79.400000000000006</v>
+        <v>78.8</v>
       </c>
       <c r="Z29">
-        <v>79.400000000000006</v>
+        <v>78.8</v>
       </c>
       <c r="AA29">
-        <v>73.5</v>
+        <v>72.7</v>
+      </c>
+      <c r="AB29">
+        <v>75.8</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>32</v>
       </c>
@@ -3963,22 +4096,22 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="G30" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="H30" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="I30">
         <v>8.4</v>
@@ -4034,8 +4167,11 @@
       <c r="Z30">
         <v>28.8</v>
       </c>
+      <c r="AA30">
+        <v>32.6</v>
+      </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>33</v>
       </c>
@@ -4043,79 +4179,82 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>388</v>
       </c>
       <c r="F31" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="G31" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="H31" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="I31">
-        <v>17.600000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="J31">
-        <v>41.2</v>
+        <v>39.9</v>
       </c>
       <c r="K31">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="L31">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="M31">
-        <v>59</v>
+        <v>58.1</v>
       </c>
       <c r="N31">
-        <v>63.9</v>
+        <v>63.1</v>
       </c>
       <c r="O31">
-        <v>69.099999999999994</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="P31">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="Q31">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="R31">
-        <v>74.2</v>
+        <v>73.7</v>
       </c>
       <c r="S31">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="T31">
-        <v>63.6</v>
+        <v>62.8</v>
       </c>
       <c r="U31">
-        <v>63</v>
+        <v>62.3</v>
       </c>
       <c r="V31">
-        <v>62.2</v>
+        <v>61.4</v>
       </c>
       <c r="W31">
-        <v>65.599999999999994</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="X31">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="Y31">
-        <v>68.8</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="Z31">
-        <v>69.7</v>
+        <v>69.3</v>
+      </c>
+      <c r="AA31">
+        <v>70.5</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>34</v>
       </c>
@@ -4123,79 +4262,82 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>389</v>
       </c>
       <c r="F32" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G32" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="H32" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="I32">
-        <v>65.099999999999994</v>
+        <v>59.6</v>
       </c>
       <c r="J32">
-        <v>65.099999999999994</v>
+        <v>59.6</v>
       </c>
       <c r="K32">
-        <v>73.3</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="L32">
-        <v>66.099999999999994</v>
+        <v>60.6</v>
       </c>
       <c r="M32">
-        <v>64.900000000000006</v>
+        <v>59.4</v>
       </c>
       <c r="N32">
-        <v>65.5</v>
+        <v>60.1</v>
       </c>
       <c r="O32">
-        <v>65</v>
+        <v>59.5</v>
       </c>
       <c r="P32">
-        <v>65.3</v>
+        <v>59.8</v>
       </c>
       <c r="Q32">
-        <v>66.7</v>
+        <v>61.3</v>
       </c>
       <c r="R32">
-        <v>68.2</v>
+        <v>62.8</v>
       </c>
       <c r="S32">
-        <v>68.7</v>
+        <v>63.4</v>
       </c>
       <c r="T32">
-        <v>68.2</v>
+        <v>62.8</v>
       </c>
       <c r="U32">
-        <v>65.900000000000006</v>
+        <v>60.5</v>
       </c>
       <c r="V32">
-        <v>67.7</v>
+        <v>62.3</v>
       </c>
       <c r="W32">
-        <v>67.900000000000006</v>
+        <v>62.5</v>
       </c>
       <c r="X32">
-        <v>66.5</v>
+        <v>61.1</v>
       </c>
       <c r="Y32">
-        <v>70.099999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="Z32">
-        <v>76.2</v>
+        <v>80.900000000000006</v>
+      </c>
+      <c r="AA32">
+        <v>81.5</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>35</v>
       </c>
@@ -4203,22 +4345,22 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="G33" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="H33" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -4277,8 +4419,11 @@
       <c r="AA33">
         <v>10.5</v>
       </c>
+      <c r="AB33">
+        <v>14.3</v>
+      </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>36</v>
       </c>
@@ -4286,82 +4431,85 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F34" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G34" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="H34" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="I34">
-        <v>12.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="J34">
-        <v>32.5</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="K34">
-        <v>34.9</v>
+        <v>40.9</v>
       </c>
       <c r="L34">
-        <v>29.8</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="M34">
-        <v>30.1</v>
+        <v>36.5</v>
       </c>
       <c r="N34">
-        <v>23.5</v>
+        <v>30.5</v>
       </c>
       <c r="O34">
-        <v>25.6</v>
+        <v>32.4</v>
       </c>
       <c r="P34">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="Q34">
-        <v>48.1</v>
+        <v>52.8</v>
       </c>
       <c r="R34">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="S34">
-        <v>12.5</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>17.3</v>
       </c>
       <c r="U34">
-        <v>19.7</v>
+        <v>27</v>
       </c>
       <c r="V34">
-        <v>18.3</v>
+        <v>25.8</v>
       </c>
       <c r="W34">
-        <v>17.600000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="X34">
-        <v>19.7</v>
+        <v>27</v>
       </c>
       <c r="Y34">
-        <v>22.8</v>
+        <v>29.9</v>
       </c>
       <c r="Z34">
-        <v>13.1</v>
+        <v>21.1</v>
       </c>
       <c r="AA34">
-        <v>16.3</v>
+        <v>23.9</v>
+      </c>
+      <c r="AB34">
+        <v>25.8</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>37</v>
       </c>
@@ -4369,22 +4517,22 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G35" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="H35" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4438,10 +4586,16 @@
         <v>43.8</v>
       </c>
       <c r="Z35">
-        <v>43.8</v>
+        <v>33.5</v>
+      </c>
+      <c r="AA35">
+        <v>23.3</v>
+      </c>
+      <c r="AB35">
+        <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>38</v>
       </c>
@@ -4449,79 +4603,82 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G36" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="H36" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="I36">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="J36">
-        <v>67.099999999999994</v>
+        <v>66.5</v>
       </c>
       <c r="K36">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="L36">
+        <v>61.1</v>
+      </c>
+      <c r="M36">
+        <v>60.5</v>
+      </c>
+      <c r="N36">
+        <v>62.3</v>
+      </c>
+      <c r="O36">
+        <v>58.7</v>
+      </c>
+      <c r="P36">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="Q36">
         <v>61.8</v>
       </c>
-      <c r="M36">
-        <v>61.2</v>
-      </c>
-      <c r="N36">
-        <v>62.9</v>
-      </c>
-      <c r="O36">
+      <c r="R36">
+        <v>63</v>
+      </c>
+      <c r="S36">
+        <v>54</v>
+      </c>
+      <c r="T36">
         <v>59.4</v>
       </c>
-      <c r="P36">
-        <v>65.2</v>
-      </c>
-      <c r="Q36">
-        <v>62.5</v>
-      </c>
-      <c r="R36">
-        <v>63.6</v>
-      </c>
-      <c r="S36">
-        <v>54.8</v>
-      </c>
-      <c r="T36">
-        <v>60.1</v>
-      </c>
       <c r="U36">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="V36">
-        <v>64.599999999999994</v>
+        <v>64</v>
       </c>
       <c r="W36">
-        <v>68.099999999999994</v>
+        <v>67.5</v>
       </c>
       <c r="X36">
-        <v>69.599999999999994</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="Y36">
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
       <c r="Z36">
-        <v>73.5</v>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="AA36">
+        <v>67.2</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -4529,82 +4686,85 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F37" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G37" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="H37" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="I37">
-        <v>39.299999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="J37">
-        <v>41.6</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="K37">
-        <v>44.5</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="L37">
-        <v>43.9</v>
+        <v>40.1</v>
       </c>
       <c r="M37">
-        <v>42.2</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="N37">
-        <v>46.2</v>
+        <v>42.6</v>
       </c>
       <c r="O37">
-        <v>48</v>
+        <v>44.4</v>
       </c>
       <c r="P37">
-        <v>32.9</v>
+        <v>28.4</v>
       </c>
       <c r="Q37">
-        <v>30.6</v>
+        <v>25.9</v>
       </c>
       <c r="R37">
-        <v>29.5</v>
+        <v>24.7</v>
       </c>
       <c r="S37">
-        <v>29.5</v>
+        <v>24.7</v>
       </c>
       <c r="T37">
-        <v>37</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="U37">
-        <v>39.9</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="V37">
-        <v>39.299999999999997</v>
+        <v>34.6</v>
       </c>
       <c r="W37">
-        <v>42.8</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="X37">
-        <v>43.4</v>
+        <v>38.9</v>
       </c>
       <c r="Y37">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="Z37">
-        <v>46.8</v>
+        <v>42.6</v>
       </c>
       <c r="AA37">
-        <v>48.6</v>
+        <v>45.1</v>
+      </c>
+      <c r="AB37">
+        <v>46.3</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>44</v>
       </c>
@@ -4612,79 +4772,82 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G38" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="H38" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="I38">
-        <v>74.599999999999994</v>
+        <v>76.3</v>
       </c>
       <c r="J38">
+        <v>77.3</v>
+      </c>
+      <c r="K38">
+        <v>77.7</v>
+      </c>
+      <c r="L38">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="M38">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="N38">
+        <v>79</v>
+      </c>
+      <c r="O38">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="P38">
         <v>75.5</v>
       </c>
-      <c r="K38">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="L38">
-        <v>76.3</v>
-      </c>
-      <c r="M38">
-        <v>76.7</v>
-      </c>
-      <c r="N38">
-        <v>77</v>
-      </c>
-      <c r="O38">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="P38">
-        <v>73.5</v>
-      </c>
       <c r="Q38">
-        <v>69.7</v>
+        <v>71.7</v>
       </c>
       <c r="R38">
-        <v>65.8</v>
+        <v>67.8</v>
       </c>
       <c r="S38">
-        <v>61.9</v>
+        <v>63.9</v>
       </c>
       <c r="T38">
-        <v>58</v>
+        <v>60.1</v>
       </c>
       <c r="U38">
-        <v>53.7</v>
+        <v>55.8</v>
       </c>
       <c r="V38">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
       <c r="W38">
-        <v>45</v>
+        <v>47.2</v>
       </c>
       <c r="X38">
-        <v>40.700000000000003</v>
+        <v>42.9</v>
       </c>
       <c r="Y38">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="Z38">
-        <v>35.9</v>
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AA38">
+        <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>57</v>
       </c>
@@ -4692,22 +4855,22 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F39" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="G39" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="H39" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4731,43 +4894,46 @@
         <v>30.6</v>
       </c>
       <c r="P39">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
       <c r="Q39">
         <v>52.2</v>
       </c>
       <c r="R39">
-        <v>56.7</v>
+        <v>57.2</v>
       </c>
       <c r="S39">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="T39">
-        <v>71.099999999999994</v>
+        <v>71.7</v>
       </c>
       <c r="U39">
-        <v>70.3</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="V39">
         <v>74.2</v>
       </c>
       <c r="W39">
-        <v>76.400000000000006</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="X39">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="Y39">
         <v>83.9</v>
       </c>
       <c r="Z39">
-        <v>90.6</v>
+        <v>91.4</v>
       </c>
       <c r="AA39">
-        <v>91.1</v>
+        <v>91.7</v>
+      </c>
+      <c r="AB39">
+        <v>86.7</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>58</v>
       </c>
@@ -4775,22 +4941,22 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>390</v>
       </c>
       <c r="F40" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G40" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="H40" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="I40">
         <v>1.5</v>
@@ -4799,58 +4965,61 @@
         <v>4</v>
       </c>
       <c r="K40">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L40">
-        <v>8.1999999999999993</v>
+        <v>8.1</v>
       </c>
       <c r="M40">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="N40">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="O40">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="P40">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="Q40">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="R40">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="S40">
-        <v>33.200000000000003</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="T40">
-        <v>34.5</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="U40">
-        <v>40.200000000000003</v>
+        <v>38.9</v>
       </c>
       <c r="V40">
-        <v>37.799999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="W40">
         <v>37.799999999999997</v>
       </c>
       <c r="X40">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="Y40">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="Z40">
-        <v>55</v>
+        <v>55.9</v>
       </c>
       <c r="AA40">
-        <v>54.1</v>
+        <v>53.8</v>
+      </c>
+      <c r="AB40">
+        <v>50.1</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>59</v>
       </c>
@@ -4858,22 +5027,22 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G41" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="H41" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4927,13 +5096,16 @@
         <v>45.4</v>
       </c>
       <c r="Z41">
-        <v>46.7</v>
+        <v>45.8</v>
       </c>
       <c r="AA41">
-        <v>47.1</v>
+        <v>46.3</v>
+      </c>
+      <c r="AB41">
+        <v>46.3</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>60</v>
       </c>
@@ -4941,22 +5113,22 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F42" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="G42" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="H42" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="I42">
         <v>0.3</v>
@@ -4980,10 +5152,10 @@
         <v>5.2</v>
       </c>
       <c r="P42">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="Q42">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="R42">
         <v>18.3</v>
@@ -4992,7 +5164,7 @@
         <v>18</v>
       </c>
       <c r="T42">
-        <v>18.3</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="U42">
         <v>18</v>
@@ -5007,16 +5179,19 @@
         <v>20.9</v>
       </c>
       <c r="Y42">
-        <v>18.600000000000001</v>
+        <v>19</v>
       </c>
       <c r="Z42">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="AA42">
+        <v>30.4</v>
+      </c>
+      <c r="AB42">
         <v>30.1</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>61</v>
       </c>
@@ -5024,55 +5199,55 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E43" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G43" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="H43" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="I43">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="J43">
-        <v>36.299999999999997</v>
+        <v>36.4</v>
       </c>
       <c r="K43">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="L43">
-        <v>34.299999999999997</v>
+        <v>34.4</v>
       </c>
       <c r="M43">
         <v>35.6</v>
       </c>
       <c r="N43">
-        <v>35.1</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="O43">
-        <v>37.700000000000003</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="P43">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="Q43">
         <v>30.9</v>
       </c>
       <c r="R43">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="S43">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T43">
         <v>41</v>
@@ -5081,13 +5256,13 @@
         <v>47.6</v>
       </c>
       <c r="V43">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="W43">
         <v>56.7</v>
       </c>
       <c r="X43">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -5096,10 +5271,13 @@
         <v>8.1</v>
       </c>
       <c r="AA43">
-        <v>44</v>
+        <v>43.8</v>
+      </c>
+      <c r="AB43">
+        <v>53.4</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>68</v>
       </c>
@@ -5107,82 +5285,85 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F44" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="G44" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="H44" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="I44">
-        <v>48.2</v>
+        <v>44.9</v>
       </c>
       <c r="J44">
-        <v>48.8</v>
+        <v>45.5</v>
       </c>
       <c r="K44">
-        <v>51.8</v>
+        <v>48.7</v>
       </c>
       <c r="L44">
-        <v>48.2</v>
+        <v>44.9</v>
       </c>
       <c r="M44">
-        <v>54.2</v>
+        <v>51.3</v>
       </c>
       <c r="N44">
-        <v>48.2</v>
+        <v>44.9</v>
       </c>
       <c r="O44">
-        <v>47</v>
+        <v>43.6</v>
       </c>
       <c r="P44">
-        <v>39.799999999999997</v>
+        <v>35.9</v>
       </c>
       <c r="Q44">
-        <v>31.9</v>
+        <v>27.6</v>
       </c>
       <c r="R44">
-        <v>30.7</v>
+        <v>26.3</v>
       </c>
       <c r="S44">
-        <v>41.6</v>
+        <v>38.5</v>
       </c>
       <c r="T44">
-        <v>47.6</v>
+        <v>44.9</v>
       </c>
       <c r="U44">
-        <v>51.8</v>
+        <v>49.4</v>
       </c>
       <c r="V44">
-        <v>59.6</v>
+        <v>57.1</v>
       </c>
       <c r="W44">
-        <v>65.099999999999994</v>
+        <v>63.5</v>
       </c>
       <c r="X44">
-        <v>67.5</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="Y44">
-        <v>54.8</v>
+        <v>58.3</v>
       </c>
       <c r="Z44">
-        <v>63.3</v>
+        <v>67.3</v>
       </c>
       <c r="AA44">
-        <v>71.099999999999994</v>
+        <v>73.7</v>
+      </c>
+      <c r="AB44">
+        <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>69</v>
       </c>
@@ -5190,79 +5371,82 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E45" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G45" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="H45" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I45">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="J45">
         <v>10.4</v>
       </c>
-      <c r="J45">
-        <v>10.8</v>
-      </c>
       <c r="K45">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="L45">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="M45">
-        <v>29.7</v>
+        <v>28.4</v>
       </c>
       <c r="N45">
-        <v>38.9</v>
+        <v>37.1</v>
       </c>
       <c r="O45">
-        <v>38</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="P45">
-        <v>37.1</v>
+        <v>35.4</v>
       </c>
       <c r="Q45">
-        <v>36.200000000000003</v>
+        <v>34.5</v>
       </c>
       <c r="R45">
-        <v>40.700000000000003</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="S45">
-        <v>45.2</v>
+        <v>43</v>
       </c>
       <c r="T45">
-        <v>49.7</v>
+        <v>47.2</v>
       </c>
       <c r="U45">
-        <v>47.1</v>
+        <v>44.8</v>
       </c>
       <c r="V45">
-        <v>44.5</v>
+        <v>42.3</v>
       </c>
       <c r="W45">
-        <v>41.9</v>
+        <v>39.9</v>
       </c>
       <c r="X45">
-        <v>41.9</v>
+        <v>35.1</v>
       </c>
       <c r="Y45">
-        <v>41.9</v>
+        <v>30.3</v>
       </c>
       <c r="Z45">
-        <v>41.9</v>
+        <v>25.5</v>
+      </c>
+      <c r="AA45">
+        <v>20.7</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>73</v>
       </c>
@@ -5270,82 +5454,82 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="G46" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="H46" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="I46">
-        <v>17.100000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="J46">
-        <v>19.100000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="K46">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
       <c r="L46">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="M46">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="N46">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="O46">
-        <v>26.8</v>
+        <v>27.8</v>
       </c>
       <c r="P46">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="Q46">
-        <v>35.4</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="R46">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="S46">
-        <v>48.5</v>
+        <v>50.2</v>
       </c>
       <c r="T46">
-        <v>45</v>
+        <v>46.5</v>
       </c>
       <c r="U46">
-        <v>45</v>
+        <v>46.5</v>
       </c>
       <c r="V46">
-        <v>39.9</v>
+        <v>41.2</v>
       </c>
       <c r="W46">
-        <v>43.2</v>
+        <v>44.6</v>
       </c>
       <c r="X46">
-        <v>39</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="Y46">
-        <v>34.9</v>
+        <v>36</v>
       </c>
       <c r="Z46">
-        <v>38.200000000000003</v>
+        <v>39.4</v>
       </c>
       <c r="AA46">
-        <v>42.4</v>
+        <v>44.9</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>74</v>
       </c>
@@ -5353,22 +5537,22 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G47" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="H47" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="I47">
         <v>9.6999999999999993</v>
@@ -5427,8 +5611,11 @@
       <c r="AA47">
         <v>53.5</v>
       </c>
+      <c r="AB47">
+        <v>49.8</v>
+      </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>75</v>
       </c>
@@ -5436,22 +5623,22 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F48" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="G48" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="H48" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="I48">
         <v>0.2</v>
@@ -5510,8 +5697,11 @@
       <c r="AA48">
         <v>3.7</v>
       </c>
+      <c r="AB48">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>76</v>
       </c>
@@ -5519,79 +5709,85 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F49" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G49" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="H49" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="I49">
-        <v>90.2</v>
+        <v>90.7</v>
       </c>
       <c r="J49">
-        <v>95.1</v>
+        <v>95.4</v>
       </c>
       <c r="K49">
         <v>100</v>
       </c>
       <c r="L49">
-        <v>81.099999999999994</v>
+        <v>82.1</v>
       </c>
       <c r="M49">
-        <v>62.3</v>
+        <v>64.3</v>
       </c>
       <c r="N49">
-        <v>72.099999999999994</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O49">
-        <v>82</v>
+        <v>82.9</v>
       </c>
       <c r="P49">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q49">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="R49">
-        <v>71.099999999999994</v>
+        <v>72.7</v>
       </c>
       <c r="S49">
-        <v>68</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="T49">
-        <v>71.2</v>
+        <v>72.7</v>
       </c>
       <c r="U49">
-        <v>74.5</v>
+        <v>75.8</v>
       </c>
       <c r="V49">
-        <v>68.099999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="W49">
-        <v>61.7</v>
+        <v>63.7</v>
       </c>
       <c r="X49">
-        <v>55.9</v>
+        <v>58.2</v>
       </c>
       <c r="Y49">
-        <v>50.1</v>
+        <v>52.7</v>
       </c>
       <c r="Z49">
-        <v>50.1</v>
+        <v>58.5</v>
+      </c>
+      <c r="AA49">
+        <v>64.3</v>
+      </c>
+      <c r="AB49">
+        <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>77</v>
       </c>
@@ -5599,22 +5795,22 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E50" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F50" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G50" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="H50" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="I50">
         <v>25.2</v>
@@ -5668,10 +5864,16 @@
         <v>55.7</v>
       </c>
       <c r="Z50">
-        <v>55.7</v>
+        <v>53.3</v>
+      </c>
+      <c r="AA50">
+        <v>51</v>
+      </c>
+      <c r="AB50">
+        <v>48.7</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>78</v>
       </c>
@@ -5679,22 +5881,22 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F51" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="G51" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="H51" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="I51">
         <v>2.8</v>
@@ -5748,10 +5950,16 @@
         <v>12.3</v>
       </c>
       <c r="Z51">
-        <v>12.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="AA51">
+        <v>16.7</v>
+      </c>
+      <c r="AB51">
+        <v>18.8</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>81</v>
       </c>
@@ -5759,22 +5967,22 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G52" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="H52" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="I52">
         <v>16.8</v>
@@ -5828,10 +6036,16 @@
         <v>52.6</v>
       </c>
       <c r="Z52">
-        <v>52.6</v>
+        <v>47.6</v>
+      </c>
+      <c r="AA52">
+        <v>42.7</v>
+      </c>
+      <c r="AB52">
+        <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>82</v>
       </c>
@@ -5839,22 +6053,22 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F53" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G53" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="H53" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="I53">
         <v>30.2</v>
@@ -5908,10 +6122,16 @@
         <v>39.4</v>
       </c>
       <c r="Z53">
-        <v>39.4</v>
+        <v>39.5</v>
+      </c>
+      <c r="AA53">
+        <v>39.5</v>
+      </c>
+      <c r="AB53">
+        <v>39.6</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>83</v>
       </c>
@@ -5919,79 +6139,82 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E54" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="G54" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="H54" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="I54">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="J54">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="K54">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="L54">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="M54">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="N54">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="O54">
-        <v>16</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="P54">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="Q54">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="R54">
+        <v>13.2</v>
+      </c>
+      <c r="S54">
         <v>12.3</v>
       </c>
-      <c r="S54">
-        <v>11.3</v>
-      </c>
       <c r="T54">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="U54">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="V54">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="W54">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y54">
-        <v>1.1000000000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Z54">
-        <v>2.1</v>
+        <v>3.2</v>
+      </c>
+      <c r="AA54">
+        <v>4.3</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>86</v>
       </c>
@@ -5999,22 +6222,22 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F55" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G55" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="H55" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="I55">
         <v>2.2999999999999998</v>
@@ -6068,10 +6291,16 @@
         <v>25.7</v>
       </c>
       <c r="Z55">
-        <v>25.7</v>
+        <v>25.8</v>
+      </c>
+      <c r="AA55">
+        <v>25.9</v>
+      </c>
+      <c r="AB55">
+        <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>87</v>
       </c>
@@ -6079,40 +6308,40 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E56" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F56" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G56" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="H56" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I56">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="J56">
         <v>7.8</v>
       </c>
       <c r="K56">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="L56">
-        <v>9.3000000000000007</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M56">
         <v>7.8</v>
       </c>
       <c r="N56">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="O56">
         <v>4.3</v>
@@ -6121,7 +6350,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="Q56">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="R56">
         <v>23.7</v>
@@ -6130,13 +6359,13 @@
         <v>35.200000000000003</v>
       </c>
       <c r="T56">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U56">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="V56">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="W56">
         <v>44.8</v>
@@ -6148,10 +6377,16 @@
         <v>23.3</v>
       </c>
       <c r="Z56">
-        <v>23.3</v>
+        <v>23.7</v>
+      </c>
+      <c r="AA56">
+        <v>24.2</v>
+      </c>
+      <c r="AB56">
+        <v>24.6</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>94</v>
       </c>
@@ -6159,22 +6394,22 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F57" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="G57" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="H57" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="I57">
         <v>11.6</v>
@@ -6228,10 +6463,16 @@
         <v>25.9</v>
       </c>
       <c r="Z57">
-        <v>25.9</v>
+        <v>26.5</v>
+      </c>
+      <c r="AA57">
+        <v>27</v>
+      </c>
+      <c r="AB57">
+        <v>27.6</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>97</v>
       </c>
@@ -6239,22 +6480,22 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F58" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G58" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="H58" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -6308,10 +6549,16 @@
         <v>45.1</v>
       </c>
       <c r="Z58">
-        <v>45.1</v>
+        <v>34.4</v>
+      </c>
+      <c r="AA58">
+        <v>23.7</v>
+      </c>
+      <c r="AB58">
+        <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>101</v>
       </c>
@@ -6319,82 +6566,85 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F59" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G59" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="H59" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="I59">
-        <v>48.7</v>
+        <v>50.1</v>
       </c>
       <c r="J59">
-        <v>49.1</v>
+        <v>50.5</v>
       </c>
       <c r="K59">
-        <v>38</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="L59">
-        <v>37.5</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="M59">
-        <v>40.6</v>
+        <v>42.3</v>
       </c>
       <c r="N59">
-        <v>37.299999999999997</v>
+        <v>38.9</v>
       </c>
       <c r="O59">
-        <v>31.4</v>
+        <v>33</v>
       </c>
       <c r="P59">
-        <v>29.9</v>
+        <v>31.6</v>
       </c>
       <c r="Q59">
-        <v>31.1</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="R59">
-        <v>32.700000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="S59">
-        <v>32.5</v>
+        <v>34.1</v>
       </c>
       <c r="T59">
-        <v>37.200000000000003</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="U59">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="V59">
+        <v>42.2</v>
+      </c>
+      <c r="W59">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="X59">
+        <v>40.5</v>
+      </c>
+      <c r="Y59">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="Z59">
         <v>36.200000000000003</v>
       </c>
-      <c r="V59">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="W59">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="X59">
-        <v>38.9</v>
-      </c>
-      <c r="Y59">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="Z59">
-        <v>34.700000000000003</v>
-      </c>
       <c r="AA59">
-        <v>34.799999999999997</v>
+        <v>35.799999999999997</v>
+      </c>
+      <c r="AB59">
+        <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>108</v>
       </c>
@@ -6402,82 +6652,85 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E60" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F60" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="G60" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="H60" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="I60">
-        <v>76</v>
+        <v>71.3</v>
       </c>
       <c r="J60">
-        <v>80.5</v>
+        <v>75.5</v>
       </c>
       <c r="K60">
-        <v>79.2</v>
+        <v>74.3</v>
       </c>
       <c r="L60">
+        <v>74.7</v>
+      </c>
+      <c r="M60">
+        <v>69.2</v>
+      </c>
+      <c r="N60">
+        <v>70</v>
+      </c>
+      <c r="O60">
+        <v>70.8</v>
+      </c>
+      <c r="P60">
+        <v>72.3</v>
+      </c>
+      <c r="Q60">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="R60">
+        <v>78.8</v>
+      </c>
+      <c r="S60">
+        <v>83.1</v>
+      </c>
+      <c r="T60">
+        <v>82.2</v>
+      </c>
+      <c r="U60">
+        <v>86.7</v>
+      </c>
+      <c r="V60">
+        <v>84.5</v>
+      </c>
+      <c r="W60">
+        <v>86.3</v>
+      </c>
+      <c r="X60">
+        <v>86.1</v>
+      </c>
+      <c r="Y60">
+        <v>93.2</v>
+      </c>
+      <c r="Z60">
+        <v>92.8</v>
+      </c>
+      <c r="AA60">
+        <v>85.3</v>
+      </c>
+      <c r="AB60">
         <v>79.7</v>
       </c>
-      <c r="M60">
-        <v>73.8</v>
-      </c>
-      <c r="N60">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="O60">
-        <v>75.3</v>
-      </c>
-      <c r="P60">
-        <v>76.8</v>
-      </c>
-      <c r="Q60">
-        <v>78.3</v>
-      </c>
-      <c r="R60">
-        <v>83</v>
-      </c>
-      <c r="S60">
-        <v>87.1</v>
-      </c>
-      <c r="T60">
-        <v>86.1</v>
-      </c>
-      <c r="U60">
-        <v>90.4</v>
-      </c>
-      <c r="V60">
-        <v>88.4</v>
-      </c>
-      <c r="W60">
-        <v>90.1</v>
-      </c>
-      <c r="X60">
-        <v>89.9</v>
-      </c>
-      <c r="Y60">
-        <v>96.6</v>
-      </c>
-      <c r="Z60">
-        <v>96.2</v>
-      </c>
-      <c r="AA60">
-        <v>84.8</v>
-      </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>109</v>
       </c>
@@ -6485,82 +6738,85 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E61" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="G61" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="H61" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="I61">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="J61">
-        <v>30</v>
+        <v>32.9</v>
       </c>
       <c r="K61">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="L61">
-        <v>36.9</v>
+        <v>40.5</v>
       </c>
       <c r="M61">
-        <v>34.299999999999997</v>
+        <v>37.6</v>
       </c>
       <c r="N61">
-        <v>34.299999999999997</v>
+        <v>37.6</v>
       </c>
       <c r="O61">
-        <v>34.299999999999997</v>
+        <v>37.6</v>
       </c>
       <c r="P61">
-        <v>54.8</v>
+        <v>57.1</v>
       </c>
       <c r="Q61">
-        <v>34.299999999999997</v>
+        <v>37.6</v>
       </c>
       <c r="R61">
-        <v>48</v>
+        <v>50.6</v>
       </c>
       <c r="S61">
-        <v>61.7</v>
+        <v>63.6</v>
       </c>
       <c r="T61">
-        <v>61.7</v>
+        <v>63.6</v>
       </c>
       <c r="U61">
-        <v>82.2</v>
+        <v>83.1</v>
       </c>
       <c r="V61">
-        <v>75.400000000000006</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="W61">
-        <v>54.8</v>
+        <v>57.1</v>
       </c>
       <c r="X61">
-        <v>68.5</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="Y61">
-        <v>68.5</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="Z61">
-        <v>75.400000000000006</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="AA61">
-        <v>68.5</v>
+        <v>70.099999999999994</v>
+      </c>
+      <c r="AB61">
+        <v>78.8</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>111</v>
       </c>
@@ -6568,79 +6824,82 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E62" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F62" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="G62" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H62" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>19.899999999999999</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="K62">
-        <v>35.6</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="L62">
-        <v>34.799999999999997</v>
+        <v>33.4</v>
       </c>
       <c r="M62">
-        <v>41.5</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="N62">
-        <v>42.8</v>
+        <v>41.1</v>
       </c>
       <c r="O62">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
       <c r="P62">
-        <v>47.3</v>
+        <v>45.3</v>
       </c>
       <c r="Q62">
-        <v>64.3</v>
+        <v>61.7</v>
       </c>
       <c r="R62">
-        <v>61.7</v>
+        <v>59.2</v>
       </c>
       <c r="S62">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="T62">
-        <v>60.6</v>
+        <v>58.2</v>
       </c>
       <c r="U62">
-        <v>64.5</v>
+        <v>61.9</v>
       </c>
       <c r="V62">
-        <v>59.2</v>
+        <v>56.8</v>
       </c>
       <c r="W62">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="X62">
-        <v>62.1</v>
+        <v>59.5</v>
       </c>
       <c r="Y62">
-        <v>71.099999999999994</v>
+        <v>68.2</v>
       </c>
       <c r="Z62">
-        <v>65.900000000000006</v>
+        <v>65.5</v>
+      </c>
+      <c r="AA62">
+        <v>58.1</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>112</v>
       </c>
@@ -6648,79 +6907,85 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E63" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F63" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="G63" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="H63" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="I63">
-        <v>59.6</v>
+        <v>54.6</v>
       </c>
       <c r="J63">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K63">
-        <v>58.5</v>
+        <v>53.3</v>
       </c>
       <c r="L63">
-        <v>45.3</v>
+        <v>38.6</v>
       </c>
       <c r="M63">
-        <v>32.200000000000003</v>
+        <v>23.8</v>
       </c>
       <c r="N63">
-        <v>31.8</v>
+        <v>23.4</v>
       </c>
       <c r="O63">
-        <v>31.4</v>
+        <v>22.9</v>
       </c>
       <c r="P63">
-        <v>37.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q63">
-        <v>43.3</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="R63">
-        <v>52.2</v>
+        <v>46.2</v>
       </c>
       <c r="S63">
-        <v>61</v>
+        <v>56.2</v>
       </c>
       <c r="T63">
-        <v>66.8</v>
+        <v>62.7</v>
       </c>
       <c r="U63">
-        <v>72.599999999999994</v>
+        <v>69.2</v>
       </c>
       <c r="V63">
-        <v>72.2</v>
+        <v>68.8</v>
       </c>
       <c r="W63">
-        <v>71.900000000000006</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="X63">
-        <v>67.2</v>
+        <v>63.1</v>
       </c>
       <c r="Y63">
-        <v>62.4</v>
+        <v>57.8</v>
       </c>
       <c r="Z63">
-        <v>62.4</v>
+        <v>57.9</v>
+      </c>
+      <c r="AA63">
+        <v>58.1</v>
+      </c>
+      <c r="AB63">
+        <v>58.2</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>113</v>
       </c>
@@ -6728,79 +6993,85 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E64" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F64" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="H64" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K64">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="L64">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="M64">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="N64">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="O64">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="P64">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="Q64">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="R64">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="S64">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="T64">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="U64">
-        <v>37.799999999999997</v>
+        <v>37</v>
       </c>
       <c r="V64">
-        <v>39.799999999999997</v>
+        <v>38.9</v>
       </c>
       <c r="W64">
-        <v>41.8</v>
+        <v>40.9</v>
       </c>
       <c r="X64">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
       <c r="Y64">
-        <v>47.9</v>
+        <v>46.9</v>
       </c>
       <c r="Z64">
-        <v>47.9</v>
+        <v>47.6</v>
+      </c>
+      <c r="AA64">
+        <v>48.4</v>
+      </c>
+      <c r="AB64">
+        <v>49.2</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>114</v>
       </c>
@@ -6808,22 +7079,22 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G65" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="H65" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="I65">
         <v>83.9</v>
@@ -6879,8 +7150,11 @@
       <c r="Z65">
         <v>99</v>
       </c>
+      <c r="AA65">
+        <v>98.9</v>
+      </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>115</v>
       </c>
@@ -6888,82 +7162,85 @@
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F66" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="G66" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="H66" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="I66">
-        <v>26.1</v>
+        <v>28.9</v>
       </c>
       <c r="J66">
-        <v>29.9</v>
+        <v>33.1</v>
       </c>
       <c r="K66">
-        <v>31.1</v>
+        <v>34.4</v>
       </c>
       <c r="L66">
-        <v>27.9</v>
+        <v>30.9</v>
       </c>
       <c r="M66">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="N66">
-        <v>32</v>
+        <v>35.4</v>
       </c>
       <c r="O66">
-        <v>37.299999999999997</v>
+        <v>41.2</v>
       </c>
       <c r="P66">
-        <v>40.200000000000003</v>
+        <v>44.5</v>
       </c>
       <c r="Q66">
-        <v>39.9</v>
+        <v>44.2</v>
       </c>
       <c r="R66">
-        <v>35.6</v>
+        <v>39.4</v>
       </c>
       <c r="S66">
-        <v>40.799999999999997</v>
+        <v>45.2</v>
       </c>
       <c r="T66">
-        <v>40.1</v>
+        <v>44.3</v>
       </c>
       <c r="U66">
-        <v>45.3</v>
+        <v>50.2</v>
       </c>
       <c r="V66">
-        <v>45.2</v>
+        <v>49.9</v>
       </c>
       <c r="W66">
-        <v>45.9</v>
+        <v>50.8</v>
       </c>
       <c r="X66">
-        <v>48.2</v>
+        <v>53.3</v>
       </c>
       <c r="Y66">
-        <v>49.4</v>
+        <v>54.6</v>
       </c>
       <c r="Z66">
-        <v>49.5</v>
+        <v>54.7</v>
       </c>
       <c r="AA66">
-        <v>51.3</v>
+        <v>56.8</v>
+      </c>
+      <c r="AB66">
+        <v>56.5</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>116</v>
       </c>
@@ -6971,22 +7248,22 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E67" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F67" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="G67" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="H67" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -7042,8 +7319,11 @@
       <c r="Z67">
         <v>62.2</v>
       </c>
+      <c r="AA67">
+        <v>64.900000000000006</v>
+      </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>117</v>
       </c>
@@ -7051,82 +7331,85 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F68" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="G68" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="H68" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="I68">
-        <v>77.3</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="J68">
-        <v>75.900000000000006</v>
+        <v>75.7</v>
       </c>
       <c r="K68">
-        <v>78.7</v>
+        <v>78.3</v>
       </c>
       <c r="L68">
-        <v>80</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="M68">
-        <v>81.3</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="N68">
-        <v>83.3</v>
+        <v>82.7</v>
       </c>
       <c r="O68">
-        <v>85.8</v>
+        <v>85.1</v>
       </c>
       <c r="P68">
+        <v>85.9</v>
+      </c>
+      <c r="Q68">
         <v>86.6</v>
       </c>
-      <c r="Q68">
+      <c r="R68">
+        <v>87.6</v>
+      </c>
+      <c r="S68">
         <v>87.4</v>
       </c>
-      <c r="R68">
-        <v>88.4</v>
-      </c>
-      <c r="S68">
-        <v>88.2</v>
-      </c>
       <c r="T68">
-        <v>85.7</v>
+        <v>85</v>
       </c>
       <c r="U68">
-        <v>87</v>
+        <v>86.1</v>
       </c>
       <c r="V68">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W68">
-        <v>85.9</v>
+        <v>84.8</v>
       </c>
       <c r="X68">
-        <v>87.9</v>
+        <v>86.6</v>
       </c>
       <c r="Y68">
-        <v>91.9</v>
+        <v>91.4</v>
       </c>
       <c r="Z68">
-        <v>92.5</v>
+        <v>92.1</v>
       </c>
       <c r="AA68">
-        <v>90.6</v>
+        <v>91</v>
+      </c>
+      <c r="AB68">
+        <v>91.5</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>118</v>
       </c>
@@ -7134,82 +7417,82 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E69" t="s">
-        <v>89</v>
+        <v>391</v>
       </c>
       <c r="F69" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="G69" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="H69" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="I69">
-        <v>43.2</v>
+        <v>22.5</v>
       </c>
       <c r="J69">
-        <v>43.8</v>
+        <v>22.5</v>
       </c>
       <c r="K69">
-        <v>53</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="L69">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="M69">
-        <v>68.599999999999994</v>
+        <v>64</v>
       </c>
       <c r="N69">
-        <v>68.099999999999994</v>
+        <v>56.8</v>
       </c>
       <c r="O69">
-        <v>78.900000000000006</v>
+        <v>65.8</v>
       </c>
       <c r="P69">
-        <v>74.599999999999994</v>
+        <v>59.5</v>
       </c>
       <c r="Q69">
-        <v>77.3</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="R69">
-        <v>79.5</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="S69">
-        <v>83</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="T69">
-        <v>79.7</v>
+        <v>66.7</v>
       </c>
       <c r="U69">
-        <v>80.099999999999994</v>
+        <v>75.7</v>
       </c>
       <c r="V69">
-        <v>72.7</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="W69">
-        <v>72.8</v>
+        <v>77.5</v>
       </c>
       <c r="X69">
-        <v>70.900000000000006</v>
+        <v>79.3</v>
       </c>
       <c r="Y69">
-        <v>77.400000000000006</v>
+        <v>77.5</v>
       </c>
       <c r="Z69">
-        <v>81.7</v>
+        <v>82.9</v>
       </c>
       <c r="AA69">
-        <v>84.8</v>
+        <v>82.9</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>119</v>
       </c>
@@ -7217,22 +7500,22 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E70" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="G70" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="H70" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="I70">
         <v>35.1</v>
@@ -7291,8 +7574,11 @@
       <c r="AA70">
         <v>18.7</v>
       </c>
+      <c r="AB70">
+        <v>19.8</v>
+      </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>120</v>
       </c>
@@ -7300,22 +7586,22 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E71" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F71" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G71" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="H71" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="I71">
         <v>51.2</v>
@@ -7354,7 +7640,7 @@
         <v>64</v>
       </c>
       <c r="U71">
-        <v>64.400000000000006</v>
+        <v>65</v>
       </c>
       <c r="V71">
         <v>61.8</v>
@@ -7371,473 +7657,491 @@
       <c r="Z71">
         <v>54.4</v>
       </c>
+      <c r="AA71">
+        <v>52.7</v>
+      </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A72">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
         <v>121</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>1</v>
       </c>
-      <c r="C72" t="s">
-        <v>109</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" t="s">
-        <v>92</v>
-      </c>
-      <c r="F72" t="s">
-        <v>261</v>
-      </c>
-      <c r="G72" t="s">
-        <v>337</v>
-      </c>
-      <c r="H72" t="s">
-        <v>390</v>
-      </c>
-      <c r="I72">
+      <c r="C72" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="I72" s="5">
         <v>29.8</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="5">
         <v>25.8</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="5">
         <v>28</v>
       </c>
-      <c r="L72">
+      <c r="L72" s="5">
         <v>19.600000000000001</v>
       </c>
-      <c r="M72">
+      <c r="M72" s="5">
         <v>43.1</v>
       </c>
-      <c r="N72">
+      <c r="N72" s="5">
         <v>34.700000000000003</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="5">
         <v>45.3</v>
       </c>
-      <c r="P72">
+      <c r="P72" s="5">
         <v>50.2</v>
       </c>
-      <c r="Q72">
+      <c r="Q72" s="5">
         <v>51.6</v>
       </c>
-      <c r="R72">
+      <c r="R72" s="5">
         <v>52</v>
       </c>
-      <c r="S72">
+      <c r="S72" s="5">
         <v>56.9</v>
       </c>
-      <c r="T72">
+      <c r="T72" s="5">
         <v>54.7</v>
       </c>
-      <c r="U72">
+      <c r="U72" s="5">
         <v>59.6</v>
       </c>
-      <c r="V72">
+      <c r="V72" s="5">
         <v>59.1</v>
       </c>
-      <c r="W72">
+      <c r="W72" s="5">
         <v>60.4</v>
       </c>
-      <c r="X72">
+      <c r="X72" s="5">
         <v>57.8</v>
       </c>
-      <c r="Y72">
+      <c r="Y72" s="5">
         <v>59.1</v>
       </c>
-      <c r="Z72">
+      <c r="Z72" s="5">
         <v>50.2</v>
       </c>
-      <c r="AA72">
+      <c r="AA72" s="5">
         <v>56.4</v>
       </c>
+      <c r="AB72" s="5">
+        <v>49.8</v>
+      </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E73" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="F73" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G73" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="H73" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="I73">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J73">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="K73">
+        <v>7.9</v>
+      </c>
+      <c r="L73">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L73">
-        <v>11.7</v>
-      </c>
       <c r="M73">
-        <v>12.1</v>
+        <v>10.5</v>
       </c>
       <c r="N73">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="O73">
-        <v>16.100000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="P73">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="Q73">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="R73">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="S73">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="T73">
-        <v>17.8</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="U73">
-        <v>19.899999999999999</v>
+        <v>20</v>
       </c>
       <c r="V73">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="W73">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="X73">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="Y73">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="Z73">
-        <v>28.4</v>
+        <v>29.3</v>
       </c>
       <c r="AA73">
-        <v>29.1</v>
+        <v>29.4</v>
+      </c>
+      <c r="AB73">
+        <v>31.2</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E74" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F74" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="H74" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I74">
-        <v>49.6</v>
+        <v>49</v>
       </c>
       <c r="J74">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="K74">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="L74">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
       <c r="M74">
-        <v>47.2</v>
+        <v>46.4</v>
       </c>
       <c r="N74">
-        <v>48.3</v>
+        <v>47.5</v>
       </c>
       <c r="O74">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="P74">
-        <v>44.5</v>
+        <v>43.4</v>
       </c>
       <c r="Q74">
-        <v>36.200000000000003</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="R74">
-        <v>30.2</v>
+        <v>28.8</v>
       </c>
       <c r="S74">
-        <v>32.5</v>
+        <v>31.3</v>
       </c>
       <c r="T74">
-        <v>41.6</v>
+        <v>40.5</v>
       </c>
       <c r="U74">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="V74">
-        <v>54.7</v>
+        <v>53.8</v>
       </c>
       <c r="W74">
-        <v>60.6</v>
+        <v>59.9</v>
       </c>
       <c r="X74">
-        <v>62.8</v>
+        <v>62.3</v>
       </c>
       <c r="Y74">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="Z74">
-        <v>63.7</v>
+        <v>63.2</v>
       </c>
       <c r="AA74">
-        <v>66</v>
+        <v>60.2</v>
+      </c>
+      <c r="AB74">
+        <v>63.8</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E75" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F75" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G75" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="H75" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="I75">
-        <v>61.2</v>
+        <v>60.7</v>
       </c>
       <c r="J75">
-        <v>57</v>
+        <v>56.8</v>
       </c>
       <c r="K75">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
       <c r="L75">
-        <v>54.1</v>
+        <v>54</v>
       </c>
       <c r="M75">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="N75">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="O75">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="P75">
-        <v>37.6</v>
+        <v>36.1</v>
       </c>
       <c r="Q75">
+        <v>26.5</v>
+      </c>
+      <c r="R75">
+        <v>22.9</v>
+      </c>
+      <c r="S75">
         <v>28.1</v>
       </c>
-      <c r="R75">
-        <v>24.4</v>
-      </c>
-      <c r="S75">
-        <v>29.1</v>
-      </c>
       <c r="T75">
-        <v>31.9</v>
+        <v>31.1</v>
       </c>
       <c r="U75">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="V75">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="W75">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="X75">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y75">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="Z75">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="AA75">
-        <v>55.2</v>
+        <v>55.3</v>
+      </c>
+      <c r="AB75">
+        <v>56.4</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E76" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F76" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="G76" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="H76" t="s">
-        <v>341</v>
-      </c>
-      <c r="I76">
-        <v>20.6</v>
-      </c>
-      <c r="J76">
-        <v>27.7</v>
-      </c>
-      <c r="K76">
-        <v>30.6</v>
-      </c>
-      <c r="L76">
-        <v>31.3</v>
-      </c>
-      <c r="M76">
-        <v>31.5</v>
-      </c>
-      <c r="N76">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="O76">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="P76">
-        <v>27.9</v>
-      </c>
-      <c r="Q76">
+        <v>330</v>
+      </c>
+      <c r="I76" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="J76" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="K76" s="7">
+        <v>28.3</v>
+      </c>
+      <c r="L76" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="M76" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="N76" s="7">
+        <v>33.1</v>
+      </c>
+      <c r="O76" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="P76" s="7">
+        <v>27.4</v>
+      </c>
+      <c r="Q76" s="7">
         <v>22</v>
       </c>
-      <c r="R76">
-        <v>20.8</v>
-      </c>
-      <c r="S76">
-        <v>24</v>
-      </c>
-      <c r="T76">
-        <v>28.7</v>
-      </c>
-      <c r="U76">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="V76">
+      <c r="R76" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="S76" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="T76" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="U76" s="7">
+        <v>32</v>
+      </c>
+      <c r="V76" s="7">
         <v>38.6</v>
       </c>
-      <c r="W76">
+      <c r="W76" s="7">
         <v>43.5</v>
       </c>
-      <c r="X76">
-        <v>46.4</v>
-      </c>
-      <c r="Y76">
-        <v>42.3</v>
-      </c>
-      <c r="Z76">
-        <v>45.7</v>
-      </c>
-      <c r="AA76">
-        <v>47.3</v>
+      <c r="X76" s="7">
+        <v>46.2</v>
+      </c>
+      <c r="Y76" s="7">
+        <v>42.8</v>
+      </c>
+      <c r="Z76" s="7">
+        <v>46.1</v>
+      </c>
+      <c r="AA76" s="7">
+        <v>46.1</v>
+      </c>
+      <c r="AB76" s="7">
+        <v>48.3</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E77" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F77" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G77" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="H77" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="I77">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="J77">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="K77">
-        <v>37.6</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="L77">
-        <v>35.799999999999997</v>
+        <v>35.6</v>
       </c>
       <c r="M77">
-        <v>37.799999999999997</v>
+        <v>37.5</v>
       </c>
       <c r="N77">
-        <v>36.9</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="O77">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="P77">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="Q77">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="R77">
-        <v>47.6</v>
+        <v>47.3</v>
       </c>
       <c r="S77">
-        <v>39.299999999999997</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="T77">
         <v>40.799999999999997</v>
       </c>
       <c r="U77">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="V77">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="W77">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="X77">
         <v>47.6</v>
@@ -7846,196 +8150,205 @@
         <v>51.6</v>
       </c>
       <c r="Z77">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="AA77">
-        <v>50.1</v>
+        <v>48.4</v>
+      </c>
+      <c r="AB77">
+        <v>49.1</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D78" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E78" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F78" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="H78" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="I78">
-        <v>57</v>
+        <v>55.8</v>
       </c>
       <c r="J78">
-        <v>58.6</v>
+        <v>57.5</v>
       </c>
       <c r="K78">
-        <v>60.2</v>
+        <v>59.2</v>
       </c>
       <c r="L78">
-        <v>60.1</v>
+        <v>59.1</v>
       </c>
       <c r="M78">
-        <v>59.4</v>
+        <v>58.4</v>
       </c>
       <c r="N78">
-        <v>61.6</v>
+        <v>60.8</v>
       </c>
       <c r="O78">
-        <v>62.7</v>
+        <v>61.9</v>
       </c>
       <c r="P78">
-        <v>53.2</v>
+        <v>52</v>
       </c>
       <c r="Q78">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
       <c r="R78">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="S78">
-        <v>45.7</v>
+        <v>44.3</v>
       </c>
       <c r="T78">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="U78">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="V78">
-        <v>44.3</v>
+        <v>43</v>
       </c>
       <c r="W78">
-        <v>43.9</v>
+        <v>42.7</v>
       </c>
       <c r="X78">
-        <v>42</v>
+        <v>40.9</v>
       </c>
       <c r="Y78">
-        <v>44.2</v>
+        <v>43.7</v>
       </c>
       <c r="Z78">
-        <v>41.3</v>
+        <v>40.4</v>
       </c>
       <c r="AA78">
-        <v>42</v>
+        <v>41.6</v>
+      </c>
+      <c r="AB78">
+        <v>42.2</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D79" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F79" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="G79" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="H79" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="I79">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="J79">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="K79">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="L79">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="M79">
-        <v>19.600000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="N79">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="O79">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="P79">
+        <v>27.8</v>
+      </c>
+      <c r="Q79">
         <v>28.3</v>
       </c>
-      <c r="Q79">
-        <v>28.9</v>
-      </c>
       <c r="R79">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="S79">
-        <v>34.700000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="T79">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="U79">
-        <v>39.700000000000003</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="V79">
-        <v>40.6</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="W79">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="X79">
-        <v>44.3</v>
+        <v>43.6</v>
       </c>
       <c r="Y79">
-        <v>38.4</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="Z79">
-        <v>43.2</v>
+        <v>42.2</v>
       </c>
       <c r="AA79">
-        <v>47.9</v>
+        <v>46.2</v>
+      </c>
+      <c r="AB79">
+        <v>45.2</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D80" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F80" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G80" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="H80" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="I80">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="J80">
         <v>32</v>
@@ -8044,446 +8357,464 @@
         <v>30.9</v>
       </c>
       <c r="L80">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="M80">
-        <v>17.399999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="N80">
-        <v>26.1</v>
+        <v>26.4</v>
       </c>
       <c r="O80">
-        <v>34.799999999999997</v>
+        <v>35</v>
       </c>
       <c r="P80">
-        <v>33.299999999999997</v>
+        <v>33.5</v>
       </c>
       <c r="Q80">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="R80">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="S80">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="T80">
-        <v>37.1</v>
+        <v>37.4</v>
       </c>
       <c r="U80">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="V80">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
       <c r="W80">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="X80">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="Y80">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="Z80">
-        <v>42</v>
+        <v>42.7</v>
       </c>
       <c r="AA80">
-        <v>42</v>
+        <v>42.8</v>
+      </c>
+      <c r="AB80">
+        <v>43</v>
       </c>
     </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E81" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F81" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G81" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="H81" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="I81">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="J81">
-        <v>17.100000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="K81">
-        <v>16.600000000000001</v>
+        <v>17</v>
       </c>
       <c r="L81">
-        <v>15.7</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="M81">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="N81">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="O81">
+        <v>14</v>
+      </c>
+      <c r="P81">
         <v>13.6</v>
       </c>
-      <c r="P81">
-        <v>13.1</v>
-      </c>
       <c r="Q81">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="R81">
-        <v>19</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="S81">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="T81">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="U81">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="V81">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="W81">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="X81">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="Y81">
-        <v>26.4</v>
+        <v>26.8</v>
       </c>
       <c r="Z81">
-        <v>26.1</v>
+        <v>25</v>
       </c>
       <c r="AA81">
-        <v>26.4</v>
+        <v>23.5</v>
+      </c>
+      <c r="AB81">
+        <v>21.6</v>
       </c>
     </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E82" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F82" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G82" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="H82" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="I82">
-        <v>32.5</v>
+        <v>31</v>
       </c>
       <c r="J82">
-        <v>39.1</v>
+        <v>37.4</v>
       </c>
       <c r="K82">
-        <v>42.1</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="L82">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="M82">
-        <v>39.200000000000003</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="N82">
-        <v>38.799999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="O82">
-        <v>38.9</v>
+        <v>36.5</v>
       </c>
       <c r="P82">
+        <v>43.7</v>
+      </c>
+      <c r="Q82">
         <v>46.1</v>
       </c>
-      <c r="Q82">
-        <v>48.3</v>
-      </c>
       <c r="R82">
-        <v>53.8</v>
+        <v>51.7</v>
       </c>
       <c r="S82">
-        <v>59.4</v>
+        <v>57.4</v>
       </c>
       <c r="T82">
-        <v>61.6</v>
+        <v>59.7</v>
       </c>
       <c r="U82">
-        <v>69.5</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="V82">
-        <v>67</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="W82">
-        <v>63.8</v>
+        <v>62.2</v>
       </c>
       <c r="X82">
-        <v>66.5</v>
+        <v>64.5</v>
       </c>
       <c r="Y82">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z82">
-        <v>69.599999999999994</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="AA82">
-        <v>66.900000000000006</v>
+        <v>64</v>
+      </c>
+      <c r="AB82">
+        <v>65</v>
       </c>
     </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E83" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F83" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="G83" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="H83" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="I83">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="J83">
-        <v>44.7</v>
+        <v>42.4</v>
       </c>
       <c r="K83">
-        <v>48.9</v>
+        <v>46.9</v>
       </c>
       <c r="L83">
-        <v>45.1</v>
+        <v>45.4</v>
       </c>
       <c r="M83">
-        <v>53.5</v>
+        <v>53.2</v>
       </c>
       <c r="N83">
-        <v>53.8</v>
+        <v>52.7</v>
       </c>
       <c r="O83">
-        <v>58.8</v>
+        <v>57.6</v>
       </c>
       <c r="P83">
-        <v>61</v>
+        <v>59.6</v>
       </c>
       <c r="Q83">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
       <c r="R83">
-        <v>63.8</v>
+        <v>62.9</v>
       </c>
       <c r="S83">
-        <v>65.099999999999994</v>
+        <v>65</v>
       </c>
       <c r="T83">
-        <v>64.8</v>
+        <v>63.6</v>
       </c>
       <c r="U83">
         <v>66.599999999999994</v>
       </c>
       <c r="V83">
-        <v>65.099999999999994</v>
+        <v>65.7</v>
       </c>
       <c r="W83">
-        <v>65.400000000000006</v>
+        <v>66.5</v>
       </c>
       <c r="X83">
-        <v>65.900000000000006</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="Y83">
-        <v>65.099999999999994</v>
+        <v>65.7</v>
       </c>
       <c r="Z83">
-        <v>61.2</v>
+        <v>61.9</v>
       </c>
       <c r="AA83">
-        <v>64.7</v>
+        <v>65.3</v>
+      </c>
+      <c r="AB83">
+        <v>66.2</v>
       </c>
     </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E84" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F84" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G84" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="H84" t="s">
-        <v>349</v>
-      </c>
-      <c r="I84">
-        <v>27.2</v>
-      </c>
-      <c r="J84">
+        <v>338</v>
+      </c>
+      <c r="I84" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="J84" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="K84" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="L84" s="7">
         <v>30.4</v>
       </c>
-      <c r="K84">
-        <v>32</v>
-      </c>
-      <c r="L84">
-        <v>30.6</v>
-      </c>
-      <c r="M84">
-        <v>30.6</v>
-      </c>
-      <c r="N84">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="O84">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="P84">
-        <v>36.1</v>
-      </c>
-      <c r="Q84">
-        <v>36.4</v>
-      </c>
-      <c r="R84">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="S84">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="T84">
-        <v>43.7</v>
-      </c>
-      <c r="U84">
-        <v>47.2</v>
-      </c>
-      <c r="V84">
-        <v>47.1</v>
-      </c>
-      <c r="W84">
-        <v>47</v>
-      </c>
-      <c r="X84">
-        <v>46.8</v>
-      </c>
-      <c r="Y84">
-        <v>46</v>
-      </c>
-      <c r="Z84">
-        <v>45.7</v>
-      </c>
-      <c r="AA84">
+      <c r="M84" s="7">
+        <v>30.3</v>
+      </c>
+      <c r="N84" s="7">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="O84" s="7">
+        <v>34.9</v>
+      </c>
+      <c r="P84" s="7">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Q84" s="7">
+        <v>36</v>
+      </c>
+      <c r="R84" s="7">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="S84" s="7">
+        <v>40</v>
+      </c>
+      <c r="T84" s="7">
+        <v>43.3</v>
+      </c>
+      <c r="U84" s="7">
+        <v>46.9</v>
+      </c>
+      <c r="V84" s="7">
+        <v>46.9</v>
+      </c>
+      <c r="W84" s="7">
+        <v>46.9</v>
+      </c>
+      <c r="X84" s="7">
         <v>46.7</v>
       </c>
+      <c r="Y84" s="7">
+        <v>45.9</v>
+      </c>
+      <c r="Z84" s="7">
+        <v>45.2</v>
+      </c>
+      <c r="AA84" s="7">
+        <v>45.3</v>
+      </c>
+      <c r="AB84" s="7">
+        <v>45</v>
+      </c>
     </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B85">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G85" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="H85" t="s">
-        <v>350</v>
-      </c>
-      <c r="I85">
-        <v>25</v>
-      </c>
-      <c r="J85">
-        <v>29.6</v>
-      </c>
-      <c r="K85">
-        <v>31.6</v>
-      </c>
-      <c r="L85">
-        <v>30.8</v>
-      </c>
-      <c r="M85">
-        <v>30.8</v>
-      </c>
-      <c r="N85">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="O85">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="P85">
-        <v>33.5</v>
-      </c>
-      <c r="Q85">
-        <v>31.3</v>
-      </c>
-      <c r="R85">
-        <v>32.4</v>
-      </c>
-      <c r="S85">
-        <v>34.5</v>
-      </c>
-      <c r="T85">
-        <v>38.5</v>
-      </c>
-      <c r="U85">
-        <v>42.1</v>
-      </c>
-      <c r="V85">
-        <v>44.4</v>
-      </c>
-      <c r="W85">
-        <v>45.9</v>
-      </c>
-      <c r="X85">
-        <v>46.7</v>
-      </c>
-      <c r="Y85">
-        <v>44.9</v>
-      </c>
-      <c r="Z85">
-        <v>45.7</v>
-      </c>
-      <c r="AA85">
-        <v>46.9</v>
+        <v>339</v>
+      </c>
+      <c r="I85" s="4">
+        <v>22.7</v>
+      </c>
+      <c r="J85" s="4">
+        <v>28.2</v>
+      </c>
+      <c r="K85" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="L85" s="4">
+        <v>30.1</v>
+      </c>
+      <c r="M85" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="N85" s="4">
+        <v>32.6</v>
+      </c>
+      <c r="O85" s="4">
+        <v>34.1</v>
+      </c>
+      <c r="P85" s="4">
+        <v>33</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>31</v>
+      </c>
+      <c r="R85" s="4">
+        <v>32</v>
+      </c>
+      <c r="S85" s="4">
+        <v>34.1</v>
+      </c>
+      <c r="T85" s="4">
+        <v>38.1</v>
+      </c>
+      <c r="U85" s="4">
+        <v>41.8</v>
+      </c>
+      <c r="V85" s="4">
+        <v>44.2</v>
+      </c>
+      <c r="W85" s="4">
+        <v>45.8</v>
+      </c>
+      <c r="X85" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="Y85" s="4">
+        <v>45</v>
+      </c>
+      <c r="Z85" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="AA85" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="AB85" s="4">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
